--- a/output/pdf_financials_xlsx/SVE.xlsx
+++ b/output/pdf_financials_xlsx/SVE.xlsx
@@ -4918,31 +4918,31 @@
         <v>0.636398</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.010596</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.257184</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.593426</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.195819</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.738722</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>4.794589</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>5.409683</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>5.933658</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>6.646053</v>
       </c>
     </row>
     <row r="93">
@@ -8017,7 +8017,11 @@
           <t>Share-based payment reserve 9(c)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -8952,7 +8956,11 @@
           <t>Share-based payment reserve 10(c)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -9414,7 +9422,11 @@
           <t>Share-based payment reserve 11(c)</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -11241,7 +11253,11 @@
           <t>Share-based payment reserve 12(c)</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -27228,7 +27244,7 @@
         </is>
       </c>
       <c r="P258" s="5" t="n">
-        <v>0.07811999999999999</v>
+        <v>-0.07811999999999999</v>
       </c>
       <c r="Q258" s="5" t="n">
         <v>-3.588923</v>

--- a/output/pdf_financials_xlsx/SVE.xlsx
+++ b/output/pdf_financials_xlsx/SVE.xlsx
@@ -2055,40 +2055,40 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.070658</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.031253</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.423334</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.30103</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.328714</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.445384</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>11.341666</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>8.708892000000001</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>3.065488</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.959557</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>2.732037</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>4.85577</v>
       </c>
     </row>
     <row r="35">
@@ -2151,40 +2151,40 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.070658</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.031253</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>2.423334</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>3.6</v>
+        <v>3.90103</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.7</v>
+        <v>1.028714</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>2.6</v>
+        <v>3.045384</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>2.51856</v>
+        <v>13.860226</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.261512</v>
+        <v>8.970404</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.266174</v>
+        <v>3.331662</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.278501</v>
+        <v>1.238058</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.066205</v>
+        <v>2.798242</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.553166</v>
+        <v>5.408936</v>
       </c>
     </row>
     <row r="37">
@@ -2727,40 +2727,40 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.072408</v>
+        <v>0.00175</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.032128</v>
+        <v>0.000875</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.474135</v>
+        <v>0.050801</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.67104</v>
+        <v>0.37001</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.523876</v>
+        <v>0.195162</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.699339</v>
+        <v>0.253955</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>18.115246</v>
+        <v>6.77358</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>11.251187</v>
+        <v>2.542295</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>4.879545</v>
+        <v>1.814057</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>2.012061</v>
+        <v>1.052504</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.917551</v>
+        <v>0.185514</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>5.016418</v>
+        <v>0.160648</v>
       </c>
     </row>
     <row r="49">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -7567,7 +7567,11 @@
           <t>Reclamation deposits 6</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -8652,7 +8656,11 @@
           <t>Reclamation deposits 7</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -9898,7 +9906,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -13334,7 +13346,11 @@
           <t>Refund of reclamation deposit</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -16016,7 +16032,11 @@
           <t>Purchase of reclamation deposit</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -16863,7 +16883,11 @@
           <t>Purchase of reclamation deposits</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -20480,7 +20504,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SVE.xlsx
+++ b/output/pdf_financials_xlsx/SVE.xlsx
@@ -711,19 +711,19 @@
         <v>0.441171</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.463136</v>
+        <v>0.523136</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.382094</v>
+        <v>0.454094</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.393382</v>
+        <v>0.471382</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.359196</v>
+        <v>0.437196</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.396833</v>
+        <v>0.474833</v>
       </c>
     </row>
     <row r="8">
@@ -855,19 +855,19 @@
         <v>0.902572</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.968716</v>
+        <v>1.028716</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.906673</v>
+        <v>0.978673</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>1.015778</v>
+        <v>1.093778</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.832856</v>
+        <v>0.910856</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.838158</v>
+        <v>0.916158</v>
       </c>
     </row>
     <row r="11">
@@ -3526,37 +3526,37 @@
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.000505</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.033451</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.514703</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.173781</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.428644</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.866617</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.413731</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.179905</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.052573</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.309228</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.297612</v>
       </c>
     </row>
     <row r="65">
@@ -3670,37 +3670,37 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.014356</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.0485</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.0325</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.0325</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.0325</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.040744</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.048344</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.0475</v>
       </c>
     </row>
     <row r="68">
@@ -5790,10 +5790,10 @@
         <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004973</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.025664</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
@@ -5994,10 +5994,10 @@
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.026722</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.234259</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
@@ -6926,10 +6926,10 @@
         <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004973</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.025664</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>0</v>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.496874</v>
+        <v>-0.501847</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-1.800348</v>
+        <v>-1.826012</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>-1.239754</v>
@@ -13656,7 +13656,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -16117,7 +16121,11 @@
           <t>Issuance of shares pursuant to private placement</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -18811,7 +18819,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -23159,7 +23171,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -26043,7 +26059,11 @@
           <t>Director fees 12</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -27517,7 +27537,11 @@
           <t>Director fees 13</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -28372,7 +28396,11 @@
           <t>Director fees 14</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -29867,7 +29895,11 @@
           <t>Director fees 15</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
